--- a/english/traducciones.xlsx
+++ b/english/traducciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\python\english\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3582BD37-397F-4E1D-92B2-3B2FB5AED79B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F482CEE0-CFF5-4763-A9E6-00FA6FDC2621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,14 +23,13 @@
   </definedNames>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="1" r:id="rId4"/>
+    <pivotCache cacheId="0" r:id="rId4"/>
   </pivotCaches>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7717" uniqueCount="5018">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7792" uniqueCount="5071">
   <si>
     <t>word</t>
   </si>
@@ -15002,9 +15001,6 @@
     <t>levantarse</t>
   </si>
   <si>
-    <t>suddenly,</t>
-  </si>
-  <si>
     <t>wand</t>
   </si>
   <si>
@@ -15023,9 +15019,6 @@
     <t>varita</t>
   </si>
   <si>
-    <t>encantamiento</t>
-  </si>
-  <si>
     <t>cansancio</t>
   </si>
   <si>
@@ -15041,9 +15034,6 @@
     <t>repentino</t>
   </si>
   <si>
-    <t>se sentó</t>
-  </si>
-  <si>
     <t>sat (sit)</t>
   </si>
   <si>
@@ -15065,15 +15055,9 @@
     <t>thick</t>
   </si>
   <si>
-    <t>duver</t>
-  </si>
-  <si>
     <t>heard (hear)</t>
   </si>
   <si>
-    <t>escuchó</t>
-  </si>
-  <si>
     <t>gasped</t>
   </si>
   <si>
@@ -15084,6 +15068,180 @@
   </si>
   <si>
     <t>squeaking</t>
+  </si>
+  <si>
+    <t>pilled</t>
+  </si>
+  <si>
+    <t>smelled</t>
+  </si>
+  <si>
+    <t>slipped</t>
+  </si>
+  <si>
+    <t>duvet</t>
+  </si>
+  <si>
+    <t>giggled</t>
+  </si>
+  <si>
+    <t>giggling</t>
+  </si>
+  <si>
+    <t>squeaky</t>
+  </si>
+  <si>
+    <t>woodlice</t>
+  </si>
+  <si>
+    <t>seat</t>
+  </si>
+  <si>
+    <t>hallway</t>
+  </si>
+  <si>
+    <t>too</t>
+  </si>
+  <si>
+    <t>bought</t>
+  </si>
+  <si>
+    <t>auction</t>
+  </si>
+  <si>
+    <t>aloud</t>
+  </si>
+  <si>
+    <t>raw</t>
+  </si>
+  <si>
+    <t>belongings</t>
+  </si>
+  <si>
+    <t>shall</t>
+  </si>
+  <si>
+    <t>cough</t>
+  </si>
+  <si>
+    <t>spring</t>
+  </si>
+  <si>
+    <t>suddenly</t>
+  </si>
+  <si>
+    <t>encanto</t>
+  </si>
+  <si>
+    <t>se sentó (sentarse)</t>
+  </si>
+  <si>
+    <t>mirando fijamente</t>
+  </si>
+  <si>
+    <t>incesante</t>
+  </si>
+  <si>
+    <t>riqueza</t>
+  </si>
+  <si>
+    <t>dureza</t>
+  </si>
+  <si>
+    <t>edredón</t>
+  </si>
+  <si>
+    <t>cálido</t>
+  </si>
+  <si>
+    <t>oyó (oír)</t>
+  </si>
+  <si>
+    <t>jadeó</t>
+  </si>
+  <si>
+    <t>evolucionando</t>
+  </si>
+  <si>
+    <t>grácil</t>
+  </si>
+  <si>
+    <t>chirrido</t>
+  </si>
+  <si>
+    <t>con bolitas (tejido)</t>
+  </si>
+  <si>
+    <t>olía</t>
+  </si>
+  <si>
+    <t>resbaló</t>
+  </si>
+  <si>
+    <t>riendo entre dientes</t>
+  </si>
+  <si>
+    <t>chirriante</t>
+  </si>
+  <si>
+    <t>rió entre dientes</t>
+  </si>
+  <si>
+    <t>cochinillas</t>
+  </si>
+  <si>
+    <t>asiento</t>
+  </si>
+  <si>
+    <t>pasillo</t>
+  </si>
+  <si>
+    <t>también</t>
+  </si>
+  <si>
+    <t>compró</t>
+  </si>
+  <si>
+    <t>subasta</t>
+  </si>
+  <si>
+    <t>ellos/ellas</t>
+  </si>
+  <si>
+    <t>conoció / se encontró</t>
+  </si>
+  <si>
+    <t>antes</t>
+  </si>
+  <si>
+    <t>en voz alta</t>
+  </si>
+  <si>
+    <t>crudo</t>
+  </si>
+  <si>
+    <t>pertenencias</t>
+  </si>
+  <si>
+    <t>deberá / voy a</t>
+  </si>
+  <si>
+    <t>tos</t>
+  </si>
+  <si>
+    <t>otro / más</t>
+  </si>
+  <si>
+    <t>jamás / alguna vez</t>
+  </si>
+  <si>
+    <t>primavera</t>
+  </si>
+  <si>
+    <t>laughed</t>
+  </si>
+  <si>
+    <t>aumentar / levantar</t>
   </si>
 </sst>
 </file>
@@ -36658,7 +36816,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{061658BE-3B1A-4888-8436-48FEB0493D88}" name="TablaDinámica1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{061658BE-3B1A-4888-8436-48FEB0493D88}" name="TablaDinámica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:D35" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
@@ -86013,10 +86171,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6B3C0A2-850D-42EC-978A-945A59BF5661}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:C125"/>
+  <dimension ref="A1:C156"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" customWidth="1"/>
+    <col min="1" max="1" width="16.140625" customWidth="1"/>
     <col min="2" max="2" width="25.7109375" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
   </cols>
@@ -86923,42 +87081,42 @@
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>4990</v>
+        <v>5032</v>
       </c>
       <c r="B103" t="s">
-        <v>5001</v>
+        <v>4999</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>4991</v>
+        <v>4990</v>
       </c>
       <c r="B104" t="s">
-        <v>4996</v>
+        <v>4995</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>4992</v>
+        <v>4991</v>
       </c>
       <c r="B105" t="s">
-        <v>4997</v>
+        <v>5033</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>4993</v>
+        <v>4992</v>
       </c>
       <c r="B106" t="s">
-        <v>4998</v>
+        <v>4996</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>4994</v>
+        <v>4993</v>
       </c>
       <c r="B107" t="s">
-        <v>5002</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -86966,101 +87124,388 @@
         <v>3347</v>
       </c>
       <c r="B108" t="s">
-        <v>4999</v>
+        <v>4997</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>4995</v>
+        <v>4994</v>
       </c>
       <c r="B109" t="s">
-        <v>5000</v>
+        <v>4998</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>5004</v>
+        <v>5001</v>
       </c>
       <c r="B110" t="s">
-        <v>5003</v>
+        <v>5034</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>5005</v>
+        <v>5002</v>
+      </c>
+      <c r="B111" t="s">
+        <v>5035</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>5006</v>
+        <v>5003</v>
+      </c>
+      <c r="B112" t="s">
+        <v>5036</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>5007</v>
+        <v>5004</v>
+      </c>
+      <c r="B113" t="s">
+        <v>3906</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>3167</v>
       </c>
+      <c r="B114" t="s">
+        <v>5037</v>
+      </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>5008</v>
+        <v>5005</v>
+      </c>
+      <c r="B115" t="s">
+        <v>3972</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>5009</v>
+        <v>5006</v>
+      </c>
+      <c r="B116" t="s">
+        <v>5038</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>5010</v>
+        <v>5007</v>
+      </c>
+      <c r="B117" t="s">
+        <v>4574</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>5011</v>
+        <v>5016</v>
+      </c>
+      <c r="B118" t="s">
+        <v>5039</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>2646</v>
       </c>
+      <c r="B119" t="s">
+        <v>5040</v>
+      </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>5012</v>
+        <v>5008</v>
       </c>
       <c r="B120" t="s">
-        <v>5013</v>
+        <v>5041</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>5014</v>
+        <v>5009</v>
+      </c>
+      <c r="B121" t="s">
+        <v>5042</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>5015</v>
+        <v>5010</v>
+      </c>
+      <c r="B122" t="s">
+        <v>5043</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>5016</v>
+        <v>5011</v>
+      </c>
+      <c r="B123" t="s">
+        <v>5044</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>5017</v>
+        <v>5012</v>
+      </c>
+      <c r="B124" t="s">
+        <v>5045</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>4332</v>
+      </c>
+      <c r="B125" t="s">
+        <v>2656</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>882</v>
+      </c>
+      <c r="B126" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>5013</v>
+      </c>
+      <c r="B127" t="s">
+        <v>5046</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>5014</v>
+      </c>
+      <c r="B128" t="s">
+        <v>5047</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>5015</v>
+      </c>
+      <c r="B129" t="s">
+        <v>5048</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>5018</v>
+      </c>
+      <c r="B130" t="s">
+        <v>5049</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>3393</v>
+      </c>
+      <c r="B131" t="s">
+        <v>3394</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>5019</v>
+      </c>
+      <c r="B132" t="s">
+        <v>5050</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>5017</v>
+      </c>
+      <c r="B133" t="s">
+        <v>5051</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>5020</v>
+      </c>
+      <c r="B134" t="s">
+        <v>5052</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>5021</v>
+      </c>
+      <c r="B135" t="s">
+        <v>5053</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>5022</v>
+      </c>
+      <c r="B136" t="s">
+        <v>5054</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>3630</v>
+      </c>
+      <c r="B137" t="s">
+        <v>3631</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>5023</v>
+      </c>
+      <c r="B138" t="s">
+        <v>5055</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>5024</v>
+      </c>
+      <c r="B139" t="s">
+        <v>5056</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>5025</v>
+      </c>
+      <c r="B140" t="s">
+        <v>5057</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>24</v>
+      </c>
+      <c r="B141" t="s">
+        <v>5058</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>3049</v>
+      </c>
+      <c r="B142" t="s">
+        <v>3050</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>73</v>
+      </c>
+      <c r="B143" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>4901</v>
+      </c>
+      <c r="B144" t="s">
+        <v>5059</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>1691</v>
+      </c>
+      <c r="B145" t="s">
+        <v>5060</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>5026</v>
+      </c>
+      <c r="B146" t="s">
+        <v>5061</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>5027</v>
+      </c>
+      <c r="B147" t="s">
+        <v>5062</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>5028</v>
+      </c>
+      <c r="B148" t="s">
+        <v>5063</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>5029</v>
+      </c>
+      <c r="B149" t="s">
+        <v>5064</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B150" t="s">
+        <v>3645</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>5030</v>
+      </c>
+      <c r="B151" t="s">
+        <v>5065</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>674</v>
+      </c>
+      <c r="B152" t="s">
+        <v>5066</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>2565</v>
+      </c>
+      <c r="B153" t="s">
+        <v>5070</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>245</v>
+      </c>
+      <c r="B154" t="s">
+        <v>5067</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>5031</v>
+      </c>
+      <c r="B155" t="s">
+        <v>5068</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>5069</v>
       </c>
     </row>
   </sheetData>

--- a/english/traducciones.xlsx
+++ b/english/traducciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\python\english\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F482CEE0-CFF5-4763-A9E6-00FA6FDC2621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A5C8795-4DC5-431C-A0C6-6C197D0495BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,20 +16,21 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Hoja1" sheetId="2" r:id="rId2"/>
     <sheet name="1000" sheetId="3" r:id="rId3"/>
+    <sheet name="Hoja2" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'1000'!$A$1:$B$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'1000'!$A$1:$C$560</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$1494</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId4"/>
+    <pivotCache cacheId="0" r:id="rId5"/>
   </pivotCaches>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7792" uniqueCount="5071">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8352" uniqueCount="5165">
   <si>
     <t>word</t>
   </si>
@@ -14770,21 +14771,9 @@
     <t>Cuenta de type2</t>
   </si>
   <si>
-    <t>concern</t>
-  </si>
-  <si>
     <t>fell</t>
   </si>
   <si>
-    <t>filed</t>
-  </si>
-  <si>
-    <t>held</t>
-  </si>
-  <si>
-    <t>rose</t>
-  </si>
-  <si>
     <t>whose</t>
   </si>
   <si>
@@ -14929,18 +14918,12 @@
     <t>parece</t>
   </si>
   <si>
-    <t>aunque / sin embargo</t>
-  </si>
-  <si>
     <t>pensó / pensamiento</t>
   </si>
   <si>
     <t>fue</t>
   </si>
   <si>
-    <t>si / ya sea que</t>
-  </si>
-  <si>
     <t>cuyo / cuya</t>
   </si>
   <si>
@@ -14962,18 +14945,6 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>slams</t>
-  </si>
-  <si>
-    <t>tapping</t>
-  </si>
-  <si>
-    <t>screaping</t>
-  </si>
-  <si>
-    <t>slate</t>
-  </si>
-  <si>
     <t>golpea</t>
   </si>
   <si>
@@ -14989,15 +14960,9 @@
     <t>peor</t>
   </si>
   <si>
-    <t>upset</t>
-  </si>
-  <si>
     <t>decepcionado</t>
   </si>
   <si>
-    <t>get up</t>
-  </si>
-  <si>
     <t>levantarse</t>
   </si>
   <si>
@@ -15242,6 +15207,324 @@
   </si>
   <si>
     <t>aumentar / levantar</t>
+  </si>
+  <si>
+    <t>stood up</t>
+  </si>
+  <si>
+    <t>cloth</t>
+  </si>
+  <si>
+    <t>wipe</t>
+  </si>
+  <si>
+    <t>whole</t>
+  </si>
+  <si>
+    <t>taps</t>
+  </si>
+  <si>
+    <t>carpets</t>
+  </si>
+  <si>
+    <t>bring</t>
+  </si>
+  <si>
+    <t>brough (bring)</t>
+  </si>
+  <si>
+    <t>were (they)</t>
+  </si>
+  <si>
+    <t>was (he)</t>
+  </si>
+  <si>
+    <t>picked up</t>
+  </si>
+  <si>
+    <t>landlord</t>
+  </si>
+  <si>
+    <t>seemed</t>
+  </si>
+  <si>
+    <t>got out</t>
+  </si>
+  <si>
+    <t>spotted</t>
+  </si>
+  <si>
+    <t>over on the right</t>
+  </si>
+  <si>
+    <t>disguised</t>
+  </si>
+  <si>
+    <t>clergyman</t>
+  </si>
+  <si>
+    <t>glanced</t>
+  </si>
+  <si>
+    <t>inlay</t>
+  </si>
+  <si>
+    <t>oak armchair</t>
+  </si>
+  <si>
+    <t>poked</t>
+  </si>
+  <si>
+    <t>se rio</t>
+  </si>
+  <si>
+    <t>se levantó</t>
+  </si>
+  <si>
+    <t>paño</t>
+  </si>
+  <si>
+    <t>limpiar</t>
+  </si>
+  <si>
+    <t>plano</t>
+  </si>
+  <si>
+    <t>entero</t>
+  </si>
+  <si>
+    <t>grifos</t>
+  </si>
+  <si>
+    <t>alfombras</t>
+  </si>
+  <si>
+    <t>traer</t>
+  </si>
+  <si>
+    <t>estaban</t>
+  </si>
+  <si>
+    <t>estaba</t>
+  </si>
+  <si>
+    <t>recogió</t>
+  </si>
+  <si>
+    <t>dueño / casero</t>
+  </si>
+  <si>
+    <t>parecía</t>
+  </si>
+  <si>
+    <t>salió</t>
+  </si>
+  <si>
+    <t>divisó</t>
+  </si>
+  <si>
+    <t>más allá</t>
+  </si>
+  <si>
+    <t>hacia la derecha</t>
+  </si>
+  <si>
+    <t>disfrazado</t>
+  </si>
+  <si>
+    <t>clérigo</t>
+  </si>
+  <si>
+    <t>echó un vistazo</t>
+  </si>
+  <si>
+    <t>incrustación</t>
+  </si>
+  <si>
+    <t>sillón de roble</t>
+  </si>
+  <si>
+    <t>tampoco / o bien</t>
+  </si>
+  <si>
+    <t>hurgó / tocó</t>
+  </si>
+  <si>
+    <t>más lejos</t>
+  </si>
+  <si>
+    <t>Learned</t>
+  </si>
+  <si>
+    <t>announced</t>
+  </si>
+  <si>
+    <t>bonus</t>
+  </si>
+  <si>
+    <t>bonds</t>
+  </si>
+  <si>
+    <t>purchase / to buy</t>
+  </si>
+  <si>
+    <t>growing / increasing</t>
+  </si>
+  <si>
+    <t>to give</t>
+  </si>
+  <si>
+    <t>below / underneath</t>
+  </si>
+  <si>
+    <t>to enjoy</t>
+  </si>
+  <si>
+    <t>above / over</t>
+  </si>
+  <si>
+    <t>efforts</t>
+  </si>
+  <si>
+    <t>outside / external</t>
+  </si>
+  <si>
+    <t>fact / done</t>
+  </si>
+  <si>
+    <t>launch / to release</t>
+  </si>
+  <si>
+    <t>less / minimum</t>
+  </si>
+  <si>
+    <t>to obtain / to get</t>
+  </si>
+  <si>
+    <t>obtained / got / received</t>
+  </si>
+  <si>
+    <t>offer</t>
+  </si>
+  <si>
+    <t>president / director</t>
+  </si>
+  <si>
+    <t>provides</t>
+  </si>
+  <si>
+    <t>can / could</t>
+  </si>
+  <si>
+    <t>according to</t>
+  </si>
+  <si>
+    <t>to rise / increase</t>
+  </si>
+  <si>
+    <t>had</t>
+  </si>
+  <si>
+    <t>once / once (that)</t>
+  </si>
+  <si>
+    <t>came / arrived</t>
+  </si>
+  <si>
+    <t>offer / bid</t>
+  </si>
+  <si>
+    <t>brought / took</t>
+  </si>
+  <si>
+    <t>case</t>
+  </si>
+  <si>
+    <t>claims</t>
+  </si>
+  <si>
+    <t>concern / issue</t>
+  </si>
+  <si>
+    <t>agreement / deal</t>
+  </si>
+  <si>
+    <t>due / scheduled</t>
+  </si>
+  <si>
+    <t>either / neither</t>
+  </si>
+  <si>
+    <t>filed / presented</t>
+  </si>
+  <si>
+    <t>previous / former</t>
+  </si>
+  <si>
+    <t>additional / further</t>
+  </si>
+  <si>
+    <t>fact</t>
+  </si>
+  <si>
+    <t>launch / release</t>
+  </si>
+  <si>
+    <t>to obtain / get</t>
+  </si>
+  <si>
+    <t>held / maintained</t>
+  </si>
+  <si>
+    <t>likely</t>
+  </si>
+  <si>
+    <t>almost</t>
+  </si>
+  <si>
+    <t>often / frequently</t>
+  </si>
+  <si>
+    <t>rather / quite</t>
+  </si>
+  <si>
+    <t>once / once that</t>
+  </si>
+  <si>
+    <t>rose / increased</t>
+  </si>
+  <si>
+    <t>seems</t>
+  </si>
+  <si>
+    <t>came</t>
+  </si>
+  <si>
+    <t>towards</t>
+  </si>
+  <si>
+    <t>still / yet</t>
+  </si>
+  <si>
+    <t>yield / to produce</t>
+  </si>
+  <si>
+    <t>hits</t>
+  </si>
+  <si>
+    <t>touching</t>
+  </si>
+  <si>
+    <t>screeching</t>
+  </si>
+  <si>
+    <t>chalkboard</t>
+  </si>
+  <si>
+    <t>to get up</t>
+  </si>
+  <si>
+    <t>smart</t>
   </si>
 </sst>
 </file>
@@ -15265,15 +15548,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -15281,11 +15570,55 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -15296,10 +15629,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -86171,1379 +86516,3935 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6B3C0A2-850D-42EC-978A-945A59BF5661}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:C156"/>
+  <dimension ref="A1:C560"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.140625" customWidth="1"/>
-    <col min="2" max="2" width="25.7109375" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="1" max="1" width="26.28515625" style="8" customWidth="1"/>
+    <col min="2" max="2" width="0.42578125" style="8" customWidth="1"/>
+    <col min="3" max="3" width="5.42578125" style="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="7" t="s">
+        <v>4915</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>4916</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>5107</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>882</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>413</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>4920</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
+        <v>3027</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>3028</v>
+      </c>
+      <c r="C4" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>401</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
+        <v>4898</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>4921</v>
+      </c>
+      <c r="C6" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>5108</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>4919</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>4920</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
-        <v>544</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="C7" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
+        <v>5133</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>4923</v>
+      </c>
+      <c r="C8" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
+        <v>5109</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>4924</v>
+      </c>
+      <c r="C9" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="8" t="s">
+        <v>5110</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>4925</v>
+      </c>
+      <c r="C10" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>5134</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>4926</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
+        <v>5111</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>4956</v>
+      </c>
+      <c r="C12" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>5135</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>4928</v>
+      </c>
+      <c r="C13" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
+        <v>5112</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>4944</v>
+      </c>
+      <c r="C14" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
+        <v>5136</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>4930</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="8" t="s">
+        <v>5137</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>4931</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="8" t="s">
+        <v>5138</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>4932</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="8" t="s">
+        <v>1561</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>1562</v>
+      </c>
+      <c r="C18" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="8" t="s">
+        <v>5113</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>4942</v>
+      </c>
+      <c r="C19" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>5139</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>4933</v>
+      </c>
+      <c r="C20" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="8" t="s">
+        <v>1479</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>4922</v>
+      </c>
+      <c r="C21" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="8" t="s">
+        <v>5140</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>4934</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="8" t="s">
+        <v>1715</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>1716</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>4935</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="8" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="8" t="s">
+        <v>5115</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>1358</v>
+      </c>
+      <c r="C27" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="8" t="s">
+        <v>401</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="8" t="s">
+        <v>4913</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>4937</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="8" t="s">
+        <v>5141</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>4938</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="6" t="s">
+        <v>5142</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>4939</v>
+      </c>
+      <c r="C31" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="8" t="s">
+        <v>5143</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>4940</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="8" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>4917</v>
+      </c>
+      <c r="C33" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="8" t="s">
+        <v>5117</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>4506</v>
+      </c>
+      <c r="C34" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="8" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>4954</v>
+      </c>
+      <c r="C35" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="8" t="s">
+        <v>5144</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>4936</v>
+      </c>
+      <c r="C36" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="8" t="s">
+        <v>5145</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>4958</v>
+      </c>
+      <c r="C37" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="8" t="s">
+        <v>5121</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>4947</v>
+      </c>
+      <c r="C38" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="8" t="s">
+        <v>5146</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>4941</v>
+      </c>
+      <c r="C39" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="8" t="s">
+        <v>5147</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>4946</v>
+      </c>
+      <c r="C40" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="8" t="s">
+        <v>5123</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>4943</v>
+      </c>
+      <c r="C41" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="8" t="s">
+        <v>5148</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>4948</v>
+      </c>
+      <c r="C42" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="8" t="s">
+        <v>3067</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>4967</v>
+      </c>
+      <c r="C43" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="8" t="s">
+        <v>5124</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>4951</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="8" t="s">
+        <v>5149</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>4950</v>
+      </c>
+      <c r="C45" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>4962</v>
+      </c>
+      <c r="C46" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="8" t="s">
+        <v>5150</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>4952</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="8" t="s">
+        <v>5125</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>4929</v>
+      </c>
+      <c r="C48" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="8" t="s">
+        <v>5126</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>4955</v>
+      </c>
+      <c r="C49" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="8" t="s">
+        <v>5127</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>4949</v>
+      </c>
+      <c r="C50" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="8" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C51" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="8" t="s">
+        <v>5128</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>4918</v>
+      </c>
+      <c r="C52" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="8" t="s">
+        <v>5151</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>4957</v>
+      </c>
+      <c r="C53" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="8" t="s">
+        <v>5129</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>4959</v>
+      </c>
+      <c r="C54" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="8" t="s">
+        <v>5130</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>4945</v>
+      </c>
+      <c r="C55" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="8" t="s">
+        <v>5152</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>4953</v>
+      </c>
+      <c r="C56" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="8" t="s">
+        <v>5153</v>
+      </c>
+      <c r="B57" s="8" t="s">
+        <v>4960</v>
+      </c>
+      <c r="C57" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="8" t="s">
+        <v>5154</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>4961</v>
+      </c>
+      <c r="C58" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="8" t="s">
+        <v>5155</v>
+      </c>
+      <c r="B59" s="8" t="s">
+        <v>4927</v>
+      </c>
+      <c r="C59" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="8" t="s">
+        <v>882</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>413</v>
+      </c>
+      <c r="C60" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B61" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="C61" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="8" t="s">
+        <v>5156</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>2626</v>
+      </c>
+      <c r="C62" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="8" t="s">
+        <v>410</v>
+      </c>
+      <c r="B63" s="8" t="s">
+        <v>4963</v>
+      </c>
+      <c r="C63" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="8" t="s">
+        <v>4914</v>
+      </c>
+      <c r="B64" s="8" t="s">
+        <v>4964</v>
+      </c>
+      <c r="C64" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="8" t="s">
+        <v>5157</v>
+      </c>
+      <c r="B65" s="8" t="s">
+        <v>4965</v>
+      </c>
+      <c r="C65" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="8" t="s">
+        <v>5158</v>
+      </c>
+      <c r="B66" s="8" t="s">
+        <v>4966</v>
+      </c>
+      <c r="C66" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="6" t="s">
+        <v>2636</v>
+      </c>
+      <c r="B67" s="8" t="s">
+        <v>2637</v>
+      </c>
+      <c r="C67" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="6" t="s">
+        <v>4968</v>
+      </c>
+      <c r="B68" s="8" t="s">
+        <v>4969</v>
+      </c>
+      <c r="C68" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="8" t="s">
+        <v>5159</v>
+      </c>
+      <c r="B69" s="8" t="s">
+        <v>4971</v>
+      </c>
+      <c r="C69" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="8" t="s">
+        <v>5160</v>
+      </c>
+      <c r="B70" s="8" t="s">
+        <v>4972</v>
+      </c>
+      <c r="C70" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="8" t="s">
+        <v>5161</v>
+      </c>
+      <c r="B71" s="8" t="s">
+        <v>4973</v>
+      </c>
+      <c r="C71" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="8" t="s">
+        <v>5162</v>
+      </c>
+      <c r="B72" s="8" t="s">
+        <v>4974</v>
+      </c>
+      <c r="C72" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="8" t="s">
+        <v>4900</v>
+      </c>
+      <c r="B73" s="8" t="s">
+        <v>4975</v>
+      </c>
+      <c r="C73" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="8" t="s">
+        <v>3353</v>
+      </c>
+      <c r="B74" s="8" t="s">
         <v>4976</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A3">
+      <c r="C74" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="8" t="s">
+        <v>5163</v>
+      </c>
+      <c r="B75" s="8" t="s">
+        <v>4977</v>
+      </c>
+      <c r="C75" s="11">
         <v>1</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>4921</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A4">
+    </row>
+    <row r="76" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="8" t="s">
+        <v>5164</v>
+      </c>
+      <c r="B76" s="8" t="s">
+        <v>3164</v>
+      </c>
+      <c r="C76" s="11">
         <v>1</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>4922</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    </row>
+    <row r="77" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C77" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="13"/>
+      <c r="B78" s="9"/>
+      <c r="C78" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="14"/>
+      <c r="B79" s="10"/>
+      <c r="C79" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="8" t="s">
+        <v>5020</v>
+      </c>
+      <c r="B80" s="8" t="s">
+        <v>4987</v>
+      </c>
+      <c r="C80" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="8" t="s">
+        <v>4978</v>
+      </c>
+      <c r="B81" s="8" t="s">
+        <v>4983</v>
+      </c>
+      <c r="C81" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="8" t="s">
+        <v>4979</v>
+      </c>
+      <c r="B82" s="8" t="s">
+        <v>5021</v>
+      </c>
+      <c r="C82" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="8" t="s">
+        <v>4980</v>
+      </c>
+      <c r="B83" s="8" t="s">
+        <v>4984</v>
+      </c>
+      <c r="C83" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="15" t="s">
+        <v>4981</v>
+      </c>
+      <c r="B84" s="15" t="s">
+        <v>4988</v>
+      </c>
+      <c r="C84" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="15" t="s">
+        <v>3347</v>
+      </c>
+      <c r="B85" s="15" t="s">
+        <v>4985</v>
+      </c>
+      <c r="C85" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="8" t="s">
+        <v>4982</v>
+      </c>
+      <c r="B86" s="8" t="s">
+        <v>4986</v>
+      </c>
+      <c r="C86" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="8" t="s">
+        <v>4989</v>
+      </c>
+      <c r="B87" s="8" t="s">
+        <v>5022</v>
+      </c>
+      <c r="C87" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="8" t="s">
+        <v>4990</v>
+      </c>
+      <c r="B88" s="8" t="s">
+        <v>5023</v>
+      </c>
+      <c r="C88" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="8" t="s">
+        <v>4991</v>
+      </c>
+      <c r="B89" s="8" t="s">
+        <v>5024</v>
+      </c>
+      <c r="C89" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="8" t="s">
+        <v>4992</v>
+      </c>
+      <c r="B90" s="8" t="s">
+        <v>3906</v>
+      </c>
+      <c r="C90" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="8" t="s">
+        <v>3167</v>
+      </c>
+      <c r="B91" s="8" t="s">
+        <v>5025</v>
+      </c>
+      <c r="C91" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="8" t="s">
+        <v>4993</v>
+      </c>
+      <c r="B92" s="8" t="s">
+        <v>3972</v>
+      </c>
+      <c r="C92" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="8" t="s">
+        <v>4994</v>
+      </c>
+      <c r="B93" s="8" t="s">
+        <v>5026</v>
+      </c>
+      <c r="C93" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="8" t="s">
+        <v>4995</v>
+      </c>
+      <c r="B94" s="8" t="s">
+        <v>4574</v>
+      </c>
+      <c r="C94" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="8" t="s">
+        <v>5004</v>
+      </c>
+      <c r="B95" s="8" t="s">
+        <v>5027</v>
+      </c>
+      <c r="C95" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="8" t="s">
+        <v>2646</v>
+      </c>
+      <c r="B96" s="8" t="s">
+        <v>5028</v>
+      </c>
+      <c r="C96" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="8" t="s">
+        <v>4996</v>
+      </c>
+      <c r="B97" s="8" t="s">
+        <v>5029</v>
+      </c>
+      <c r="C97" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="8" t="s">
+        <v>4997</v>
+      </c>
+      <c r="B98" s="8" t="s">
+        <v>5030</v>
+      </c>
+      <c r="C98" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="8" t="s">
+        <v>4998</v>
+      </c>
+      <c r="B99" s="8" t="s">
+        <v>5031</v>
+      </c>
+      <c r="C99" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="8" t="s">
+        <v>4999</v>
+      </c>
+      <c r="B100" s="8" t="s">
+        <v>5032</v>
+      </c>
+      <c r="C100" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="8" t="s">
+        <v>5000</v>
+      </c>
+      <c r="B101" s="8" t="s">
+        <v>5033</v>
+      </c>
+      <c r="C101" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="8" t="s">
+        <v>4332</v>
+      </c>
+      <c r="B102" s="8" t="s">
+        <v>2656</v>
+      </c>
+      <c r="C102" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="8" t="s">
         <v>882</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B103" s="8" t="s">
         <v>413</v>
       </c>
-      <c r="C5" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>4923</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>1853</v>
-      </c>
-      <c r="B7" t="s">
-        <v>4924</v>
-      </c>
-      <c r="C7" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>1</v>
-      </c>
-      <c r="B8" t="s">
-        <v>3028</v>
-      </c>
-      <c r="C8" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>1</v>
-      </c>
-      <c r="B9" t="s">
-        <v>285</v>
-      </c>
-      <c r="C9" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
-        <v>4925</v>
-      </c>
-      <c r="C10" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>1</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>4926</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
-        <v>4927</v>
-      </c>
-      <c r="C12" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>1</v>
-      </c>
-      <c r="B13" t="s">
-        <v>4928</v>
-      </c>
-      <c r="C13" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>1</v>
-      </c>
-      <c r="B14" t="s">
-        <v>4929</v>
-      </c>
-      <c r="C14" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>1154</v>
-      </c>
-      <c r="B15" t="s">
-        <v>4930</v>
-      </c>
-      <c r="C15" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>1</v>
-      </c>
-      <c r="B16" t="s">
-        <v>4931</v>
-      </c>
-      <c r="C16" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B17" t="s">
-        <v>4932</v>
-      </c>
-      <c r="C17" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>1</v>
-      </c>
-      <c r="B18" t="s">
-        <v>4933</v>
-      </c>
-      <c r="C18" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B19" t="s">
-        <v>4934</v>
-      </c>
-      <c r="C19" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>4913</v>
-      </c>
-      <c r="B20" t="s">
-        <v>4935</v>
-      </c>
-      <c r="C20" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>816</v>
-      </c>
-      <c r="B21" t="s">
-        <v>4936</v>
-      </c>
-      <c r="C21" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>1</v>
-      </c>
-      <c r="B22" s="7"/>
-    </row>
-    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>1</v>
-      </c>
-      <c r="B23" s="7"/>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>738</v>
-      </c>
-      <c r="B24" t="s">
-        <v>4937</v>
-      </c>
-      <c r="C24" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>1</v>
-      </c>
-      <c r="B25" t="s">
-        <v>4506</v>
-      </c>
-      <c r="C25" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="C103" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="8" t="s">
+        <v>5001</v>
+      </c>
+      <c r="B104" s="8" t="s">
+        <v>5034</v>
+      </c>
+      <c r="C104" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" s="8" t="s">
+        <v>5002</v>
+      </c>
+      <c r="B105" s="8" t="s">
+        <v>5035</v>
+      </c>
+      <c r="C105" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" s="8" t="s">
+        <v>5003</v>
+      </c>
+      <c r="B106" s="8" t="s">
+        <v>5036</v>
+      </c>
+      <c r="C106" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="8" t="s">
+        <v>5006</v>
+      </c>
+      <c r="B107" s="8" t="s">
+        <v>5037</v>
+      </c>
+      <c r="C107" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" s="8" t="s">
+        <v>3393</v>
+      </c>
+      <c r="B108" s="8" t="s">
+        <v>3394</v>
+      </c>
+      <c r="C108" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" s="8" t="s">
+        <v>5007</v>
+      </c>
+      <c r="B109" s="8" t="s">
+        <v>5038</v>
+      </c>
+      <c r="C109" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" s="8" t="s">
+        <v>5005</v>
+      </c>
+      <c r="B110" s="8" t="s">
+        <v>5039</v>
+      </c>
+      <c r="C110" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" s="8" t="s">
+        <v>5008</v>
+      </c>
+      <c r="B111" s="8" t="s">
+        <v>5040</v>
+      </c>
+      <c r="C111" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" s="8" t="s">
+        <v>5009</v>
+      </c>
+      <c r="B112" s="8" t="s">
+        <v>5041</v>
+      </c>
+      <c r="C112" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" s="8" t="s">
+        <v>5010</v>
+      </c>
+      <c r="B113" s="8" t="s">
+        <v>5042</v>
+      </c>
+      <c r="C113" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" s="8" t="s">
+        <v>3630</v>
+      </c>
+      <c r="B114" s="8" t="s">
+        <v>3631</v>
+      </c>
+      <c r="C114" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" s="8" t="s">
+        <v>5011</v>
+      </c>
+      <c r="B115" s="8" t="s">
+        <v>5043</v>
+      </c>
+      <c r="C115" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" s="8" t="s">
+        <v>5012</v>
+      </c>
+      <c r="B116" s="8" t="s">
+        <v>5044</v>
+      </c>
+      <c r="C116" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" s="8" t="s">
+        <v>5013</v>
+      </c>
+      <c r="B117" s="8" t="s">
+        <v>5045</v>
+      </c>
+      <c r="C117" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B118" s="8" t="s">
+        <v>5046</v>
+      </c>
+      <c r="C118" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" s="8" t="s">
+        <v>3049</v>
+      </c>
+      <c r="B119" s="8" t="s">
+        <v>3050</v>
+      </c>
+      <c r="C119" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B120" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="C120" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" s="8" t="s">
+        <v>4901</v>
+      </c>
+      <c r="B121" s="8" t="s">
+        <v>5047</v>
+      </c>
+      <c r="C121" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" s="8" t="s">
+        <v>1691</v>
+      </c>
+      <c r="B122" s="8" t="s">
+        <v>5048</v>
+      </c>
+      <c r="C122" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" s="8" t="s">
+        <v>5014</v>
+      </c>
+      <c r="B123" s="8" t="s">
+        <v>5049</v>
+      </c>
+      <c r="C123" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" s="8" t="s">
+        <v>5015</v>
+      </c>
+      <c r="B124" s="8" t="s">
+        <v>5050</v>
+      </c>
+      <c r="C124" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" s="8" t="s">
+        <v>5016</v>
+      </c>
+      <c r="B125" s="8" t="s">
+        <v>5051</v>
+      </c>
+      <c r="C125" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" s="8" t="s">
+        <v>5017</v>
+      </c>
+      <c r="B126" s="8" t="s">
+        <v>5052</v>
+      </c>
+      <c r="C126" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" s="8" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B127" s="8" t="s">
+        <v>3645</v>
+      </c>
+      <c r="C127" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" s="8" t="s">
+        <v>5018</v>
+      </c>
+      <c r="B128" s="8" t="s">
+        <v>5053</v>
+      </c>
+      <c r="C128" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" s="8" t="s">
+        <v>674</v>
+      </c>
+      <c r="B129" s="8" t="s">
+        <v>5054</v>
+      </c>
+      <c r="C129" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" s="8" t="s">
+        <v>2565</v>
+      </c>
+      <c r="B130" s="8" t="s">
+        <v>5058</v>
+      </c>
+      <c r="C130" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="B131" s="8" t="s">
+        <v>5055</v>
+      </c>
+      <c r="C131" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" s="8" t="s">
+        <v>5019</v>
+      </c>
+      <c r="B132" s="8" t="s">
+        <v>5056</v>
+      </c>
+      <c r="C132" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" s="8" t="s">
+        <v>5057</v>
+      </c>
+      <c r="B133" s="8" t="s">
+        <v>5081</v>
+      </c>
+      <c r="C133" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" s="8" t="s">
+        <v>5059</v>
+      </c>
+      <c r="B134" s="8" t="s">
+        <v>5082</v>
+      </c>
+      <c r="C134" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" s="8" t="s">
+        <v>5060</v>
+      </c>
+      <c r="B135" s="8" t="s">
+        <v>5083</v>
+      </c>
+      <c r="C135" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" s="8" t="s">
+        <v>5061</v>
+      </c>
+      <c r="B136" s="8" t="s">
+        <v>5084</v>
+      </c>
+      <c r="C136" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" s="8" t="s">
+        <v>2633</v>
+      </c>
+      <c r="B137" s="8" t="s">
+        <v>5085</v>
+      </c>
+      <c r="C137" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" s="8" t="s">
+        <v>5062</v>
+      </c>
+      <c r="B138" s="8" t="s">
+        <v>5086</v>
+      </c>
+      <c r="C138" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" s="8" t="s">
+        <v>5063</v>
+      </c>
+      <c r="B139" s="8" t="s">
+        <v>5087</v>
+      </c>
+      <c r="C139" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" s="8" t="s">
+        <v>5064</v>
+      </c>
+      <c r="B140" s="8" t="s">
+        <v>5088</v>
+      </c>
+      <c r="C140" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" s="8" t="s">
+        <v>5065</v>
+      </c>
+      <c r="B141" s="8" t="s">
+        <v>5089</v>
+      </c>
+      <c r="C141" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" s="8" t="s">
+        <v>5066</v>
+      </c>
+      <c r="B142" s="8" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C142" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" s="8" t="s">
+        <v>5067</v>
+      </c>
+      <c r="B143" s="8" t="s">
+        <v>5090</v>
+      </c>
+      <c r="C143" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" s="8" t="s">
+        <v>5068</v>
+      </c>
+      <c r="B144" s="8" t="s">
+        <v>5091</v>
+      </c>
+      <c r="C144" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" s="8" t="s">
+        <v>5069</v>
+      </c>
+      <c r="B145" s="8" t="s">
+        <v>5092</v>
+      </c>
+      <c r="C145" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" s="8" t="s">
+        <v>5070</v>
+      </c>
+      <c r="B146" s="8" t="s">
+        <v>5093</v>
+      </c>
+      <c r="C146" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" s="8" t="s">
+        <v>5071</v>
+      </c>
+      <c r="B147" s="8" t="s">
+        <v>5094</v>
+      </c>
+      <c r="C147" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" s="8" t="s">
+        <v>5072</v>
+      </c>
+      <c r="B148" s="8" t="s">
+        <v>5095</v>
+      </c>
+      <c r="C148" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" s="8" t="s">
+        <v>5073</v>
+      </c>
+      <c r="B149" s="8" t="s">
+        <v>5096</v>
+      </c>
+      <c r="C149" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" s="8" t="s">
+        <v>1699</v>
+      </c>
+      <c r="B150" s="8" t="s">
+        <v>5097</v>
+      </c>
+      <c r="C150" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" s="8" t="s">
+        <v>5074</v>
+      </c>
+      <c r="B151" s="8" t="s">
+        <v>5098</v>
+      </c>
+      <c r="C151" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" s="8" t="s">
+        <v>5075</v>
+      </c>
+      <c r="B152" s="8" t="s">
+        <v>5099</v>
+      </c>
+      <c r="C152" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" s="8" t="s">
+        <v>5076</v>
+      </c>
+      <c r="B153" s="8" t="s">
+        <v>5100</v>
+      </c>
+      <c r="C153" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" s="8" t="s">
+        <v>1634</v>
+      </c>
+      <c r="B154" s="8" t="s">
+        <v>4950</v>
+      </c>
+      <c r="C154" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" s="8" t="s">
+        <v>5077</v>
+      </c>
+      <c r="B155" s="8" t="s">
+        <v>5101</v>
+      </c>
+      <c r="C155" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" s="8" t="s">
+        <v>5078</v>
+      </c>
+      <c r="B156" s="8" t="s">
+        <v>5102</v>
+      </c>
+      <c r="C156" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" s="8" t="s">
+        <v>5079</v>
+      </c>
+      <c r="B157" s="8" t="s">
+        <v>5103</v>
+      </c>
+      <c r="C157" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" s="8" t="s">
         <v>790</v>
       </c>
-      <c r="B26" t="s">
-        <v>4938</v>
-      </c>
-      <c r="C26" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>1</v>
-      </c>
-      <c r="B27" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>73</v>
-      </c>
-      <c r="B28" t="s">
-        <v>4939</v>
-      </c>
-      <c r="C28" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>1</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>1358</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>245</v>
-      </c>
-      <c r="B30" t="s">
-        <v>246</v>
-      </c>
-      <c r="C30" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>1</v>
-      </c>
-      <c r="B31" t="s">
-        <v>4940</v>
-      </c>
-      <c r="C31" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B32" t="s">
-        <v>285</v>
-      </c>
-      <c r="C32" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>4914</v>
-      </c>
-      <c r="B33" t="s">
-        <v>4941</v>
-      </c>
-      <c r="C33" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>4915</v>
-      </c>
-      <c r="B34" t="s">
-        <v>4942</v>
-      </c>
-      <c r="C34" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>948</v>
-      </c>
-      <c r="B35" t="s">
-        <v>4943</v>
-      </c>
-      <c r="C35" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+      <c r="B158" s="8" t="s">
+        <v>5104</v>
+      </c>
+      <c r="C158" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" s="8" t="s">
+        <v>5080</v>
+      </c>
+      <c r="B159" s="8" t="s">
+        <v>5105</v>
+      </c>
+      <c r="C159" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" s="8" t="s">
         <v>840</v>
       </c>
-      <c r="B36" t="s">
-        <v>4944</v>
-      </c>
-      <c r="C36" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>1</v>
-      </c>
-      <c r="B37" t="s">
-        <v>1028</v>
-      </c>
-      <c r="C37" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>1</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>4945</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <v>1</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>4946</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>1</v>
-      </c>
-      <c r="B40" t="s">
-        <v>4947</v>
-      </c>
-      <c r="C40" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>1</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>4948</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A42">
-        <v>1</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>1562</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A43">
-        <v>1</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>4949</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>4916</v>
-      </c>
-      <c r="B44" t="s">
-        <v>4950</v>
-      </c>
-      <c r="C44" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C45" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A46">
-        <v>1</v>
-      </c>
-      <c r="B46" t="s">
-        <v>4951</v>
-      </c>
-      <c r="C46" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B47" t="s">
-        <v>4952</v>
-      </c>
-      <c r="C47" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B48" t="s">
-        <v>4973</v>
-      </c>
-      <c r="C48" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A49">
-        <v>1</v>
-      </c>
-      <c r="B49" t="s">
-        <v>4953</v>
-      </c>
-      <c r="C49" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>1634</v>
-      </c>
-      <c r="B50" t="s">
-        <v>4954</v>
-      </c>
-      <c r="C50" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A51">
-        <v>1</v>
-      </c>
-      <c r="B51" t="s">
-        <v>4955</v>
-      </c>
-      <c r="C51" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>622</v>
-      </c>
-      <c r="B52" t="s">
-        <v>4956</v>
-      </c>
-      <c r="C52" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A53">
-        <v>1</v>
-      </c>
-      <c r="B53" s="7" t="s">
-        <v>4957</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A54">
-        <v>1</v>
-      </c>
-      <c r="B54" s="7" t="s">
-        <v>4958</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A55">
-        <v>1</v>
-      </c>
-      <c r="B55" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A56">
-        <v>1</v>
-      </c>
-      <c r="B56" t="s">
-        <v>4959</v>
-      </c>
-      <c r="C56" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A57">
-        <v>1</v>
-      </c>
-      <c r="B57" s="7" t="s">
-        <v>4960</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>822</v>
-      </c>
-      <c r="B58" t="s">
-        <v>4961</v>
-      </c>
-      <c r="C58" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A59">
-        <v>1</v>
-      </c>
-      <c r="B59" s="7" t="s">
-        <v>1177</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A60">
-        <v>1</v>
-      </c>
-      <c r="B60" s="7" t="s">
-        <v>4962</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A61">
-        <v>1</v>
-      </c>
-      <c r="B61" t="s">
-        <v>4963</v>
-      </c>
-      <c r="C61" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>4917</v>
-      </c>
-      <c r="B62" t="s">
-        <v>4964</v>
-      </c>
-      <c r="C62" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B63" t="s">
-        <v>4965</v>
-      </c>
-      <c r="C63" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A64">
-        <v>1</v>
-      </c>
-      <c r="B64" t="s">
-        <v>1716</v>
-      </c>
-      <c r="C64" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>412</v>
-      </c>
-      <c r="B65" t="s">
-        <v>4966</v>
-      </c>
-      <c r="C65" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A66">
-        <v>1</v>
-      </c>
-      <c r="B66" t="s">
-        <v>4967</v>
-      </c>
-      <c r="C66" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>124</v>
-      </c>
-      <c r="B67" t="s">
-        <v>125</v>
-      </c>
-      <c r="C67" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A68">
-        <v>1</v>
-      </c>
-      <c r="B68" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A69">
-        <v>1</v>
-      </c>
-      <c r="B69" s="7" t="s">
-        <v>2626</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A70">
-        <v>1</v>
-      </c>
-      <c r="B70" s="7" t="s">
-        <v>4968</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>810</v>
-      </c>
-      <c r="B71" t="s">
-        <v>4969</v>
-      </c>
-      <c r="C71" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>4918</v>
-      </c>
-      <c r="B72" t="s">
+      <c r="B160" s="8" t="s">
+        <v>5106</v>
+      </c>
+      <c r="C160" s="11" t="s">
         <v>4970</v>
       </c>
-      <c r="C72" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>357</v>
-      </c>
-      <c r="B73" t="s">
-        <v>4971</v>
-      </c>
-      <c r="C73" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B74" t="s">
-        <v>4972</v>
-      </c>
-      <c r="C74" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>2636</v>
-      </c>
-      <c r="B75" t="s">
-        <v>2637</v>
-      </c>
-      <c r="C75" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>4974</v>
-      </c>
-      <c r="B76" t="s">
-        <v>4975</v>
-      </c>
-      <c r="C76" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C77" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>4977</v>
-      </c>
-      <c r="B78" t="s">
-        <v>4981</v>
-      </c>
-      <c r="C78" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>4978</v>
-      </c>
-      <c r="B79" t="s">
-        <v>4982</v>
-      </c>
-      <c r="C79" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>4979</v>
-      </c>
-      <c r="B80" t="s">
-        <v>4983</v>
-      </c>
-      <c r="C80" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>4980</v>
-      </c>
-      <c r="B81" t="s">
-        <v>4984</v>
-      </c>
-      <c r="C81" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>4900</v>
-      </c>
-      <c r="B82" t="s">
-        <v>4985</v>
-      </c>
-      <c r="C82" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>4986</v>
-      </c>
-      <c r="B83" t="s">
-        <v>4987</v>
-      </c>
-      <c r="C83" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>4988</v>
-      </c>
-      <c r="B84" t="s">
-        <v>4989</v>
-      </c>
-      <c r="C84" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C85" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>3750</v>
-      </c>
-      <c r="B86" t="s">
-        <v>3164</v>
-      </c>
-      <c r="C86" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C87" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C88" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C89" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C90" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C91" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C92" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C93" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C94" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C95" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C96" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C97" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C98" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C99" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C100" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C101" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
-        <v>5032</v>
-      </c>
-      <c r="B103" t="s">
-        <v>4999</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>4990</v>
-      </c>
-      <c r="B104" t="s">
-        <v>4995</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>4991</v>
-      </c>
-      <c r="B105" t="s">
-        <v>5033</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
-        <v>4992</v>
-      </c>
-      <c r="B106" t="s">
-        <v>4996</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
-        <v>4993</v>
-      </c>
-      <c r="B107" t="s">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
-        <v>3347</v>
-      </c>
-      <c r="B108" t="s">
-        <v>4997</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
-        <v>4994</v>
-      </c>
-      <c r="B109" t="s">
-        <v>4998</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
-        <v>5001</v>
-      </c>
-      <c r="B110" t="s">
-        <v>5034</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
-        <v>5002</v>
-      </c>
-      <c r="B111" t="s">
-        <v>5035</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
-        <v>5003</v>
-      </c>
-      <c r="B112" t="s">
-        <v>5036</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
-        <v>5004</v>
-      </c>
-      <c r="B113" t="s">
-        <v>3906</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
-        <v>3167</v>
-      </c>
-      <c r="B114" t="s">
-        <v>5037</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
-        <v>5005</v>
-      </c>
-      <c r="B115" t="s">
-        <v>3972</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
-        <v>5006</v>
-      </c>
-      <c r="B116" t="s">
-        <v>5038</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
-        <v>5007</v>
-      </c>
-      <c r="B117" t="s">
-        <v>4574</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
-        <v>5016</v>
-      </c>
-      <c r="B118" t="s">
-        <v>5039</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
-        <v>2646</v>
-      </c>
-      <c r="B119" t="s">
-        <v>5040</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A120" t="s">
-        <v>5008</v>
-      </c>
-      <c r="B120" t="s">
-        <v>5041</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
-        <v>5009</v>
-      </c>
-      <c r="B121" t="s">
-        <v>5042</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
-        <v>5010</v>
-      </c>
-      <c r="B122" t="s">
-        <v>5043</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
-        <v>5011</v>
-      </c>
-      <c r="B123" t="s">
-        <v>5044</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
-        <v>5012</v>
-      </c>
-      <c r="B124" t="s">
-        <v>5045</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A125" t="s">
-        <v>4332</v>
-      </c>
-      <c r="B125" t="s">
-        <v>2656</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A126" t="s">
-        <v>882</v>
-      </c>
-      <c r="B126" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
-        <v>5013</v>
-      </c>
-      <c r="B127" t="s">
-        <v>5046</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A128" t="s">
-        <v>5014</v>
-      </c>
-      <c r="B128" t="s">
-        <v>5047</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
-        <v>5015</v>
-      </c>
-      <c r="B129" t="s">
-        <v>5048</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A130" t="s">
-        <v>5018</v>
-      </c>
-      <c r="B130" t="s">
-        <v>5049</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
-        <v>3393</v>
-      </c>
-      <c r="B131" t="s">
-        <v>3394</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
-        <v>5019</v>
-      </c>
-      <c r="B132" t="s">
-        <v>5050</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
-        <v>5017</v>
-      </c>
-      <c r="B133" t="s">
-        <v>5051</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A134" t="s">
-        <v>5020</v>
-      </c>
-      <c r="B134" t="s">
-        <v>5052</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A135" t="s">
-        <v>5021</v>
-      </c>
-      <c r="B135" t="s">
-        <v>5053</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A136" t="s">
-        <v>5022</v>
-      </c>
-      <c r="B136" t="s">
-        <v>5054</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A137" t="s">
-        <v>3630</v>
-      </c>
-      <c r="B137" t="s">
-        <v>3631</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
-        <v>5023</v>
-      </c>
-      <c r="B138" t="s">
-        <v>5055</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A139" t="s">
-        <v>5024</v>
-      </c>
-      <c r="B139" t="s">
-        <v>5056</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A140" t="s">
-        <v>5025</v>
-      </c>
-      <c r="B140" t="s">
-        <v>5057</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A141" t="s">
-        <v>24</v>
-      </c>
-      <c r="B141" t="s">
-        <v>5058</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A142" t="s">
-        <v>3049</v>
-      </c>
-      <c r="B142" t="s">
-        <v>3050</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A143" t="s">
-        <v>73</v>
-      </c>
-      <c r="B143" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A144" t="s">
-        <v>4901</v>
-      </c>
-      <c r="B144" t="s">
-        <v>5059</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A145" t="s">
-        <v>1691</v>
-      </c>
-      <c r="B145" t="s">
-        <v>5060</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A146" t="s">
-        <v>5026</v>
-      </c>
-      <c r="B146" t="s">
-        <v>5061</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A147" t="s">
-        <v>5027</v>
-      </c>
-      <c r="B147" t="s">
-        <v>5062</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A148" t="s">
-        <v>5028</v>
-      </c>
-      <c r="B148" t="s">
-        <v>5063</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A149" t="s">
-        <v>5029</v>
-      </c>
-      <c r="B149" t="s">
-        <v>5064</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A150" t="s">
-        <v>1210</v>
-      </c>
-      <c r="B150" t="s">
-        <v>3645</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A151" t="s">
-        <v>5030</v>
-      </c>
-      <c r="B151" t="s">
-        <v>5065</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A152" t="s">
-        <v>674</v>
-      </c>
-      <c r="B152" t="s">
-        <v>5066</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A153" t="s">
-        <v>2565</v>
-      </c>
-      <c r="B153" t="s">
-        <v>5070</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A154" t="s">
-        <v>245</v>
-      </c>
-      <c r="B154" t="s">
-        <v>5067</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A155" t="s">
-        <v>5031</v>
-      </c>
-      <c r="B155" t="s">
-        <v>5068</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A156" t="s">
-        <v>5069</v>
+    </row>
+    <row r="161" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C161" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="162" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C162" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="163" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C163" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="164" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C164" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="165" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C165" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="166" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C166" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="167" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C167" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="168" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C168" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="169" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C169" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="170" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C170" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="171" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C171" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="172" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C172" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="173" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C173" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="174" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C174" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="175" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C175" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="176" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C176" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="177" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C177" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="178" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C178" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="179" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C179" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="180" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C180" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="181" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C181" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="182" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C182" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="183" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C183" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="184" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C184" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="185" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C185" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="186" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C186" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="187" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C187" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="188" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C188" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="189" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C189" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="190" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C190" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="191" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C191" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="192" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C192" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="193" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C193" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="194" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C194" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="195" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C195" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="196" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C196" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="197" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C197" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="198" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C198" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="199" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C199" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="200" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C200" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="201" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C201" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="202" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C202" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="203" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C203" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="204" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C204" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="205" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C205" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="206" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C206" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="207" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C207" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="208" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C208" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="209" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C209" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="210" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C210" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="211" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C211" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="212" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C212" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="213" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C213" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="214" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C214" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="215" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C215" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="216" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C216" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="217" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C217" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="218" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C218" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="219" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C219" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="220" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C220" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="221" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C221" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="222" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C222" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="223" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C223" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="224" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C224" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="225" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C225" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="226" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C226" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="227" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C227" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="228" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C228" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="229" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C229" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="230" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C230" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="231" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C231" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="232" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C232" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="233" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C233" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="234" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C234" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="235" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C235" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="236" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C236" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="237" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C237" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="238" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C238" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="239" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C239" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="240" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C240" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="241" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C241" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="242" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C242" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="243" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C243" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="244" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C244" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="245" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C245" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="246" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C246" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="247" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C247" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="248" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C248" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="249" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C249" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="250" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C250" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="251" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C251" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="252" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C252" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="253" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C253" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="254" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C254" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="255" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C255" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="256" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C256" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="257" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C257" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="258" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C258" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="259" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C259" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="260" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C260" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="261" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C261" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="262" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C262" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="263" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C263" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="264" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C264" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="265" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C265" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="266" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C266" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="267" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C267" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="268" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C268" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="269" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C269" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="270" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C270" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="271" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C271" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="272" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C272" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="273" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C273" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="274" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C274" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="275" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C275" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="276" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C276" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="277" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C277" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="278" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C278" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="279" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C279" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="280" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C280" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="281" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C281" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="282" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C282" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="283" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C283" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="284" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C284" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="285" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C285" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="286" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C286" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="287" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C287" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="288" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C288" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="289" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C289" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="290" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C290" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="291" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C291" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="292" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C292" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="293" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C293" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="294" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C294" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="295" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C295" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="296" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C296" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="297" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C297" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="298" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C298" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="299" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C299" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="300" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C300" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="301" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C301" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="302" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C302" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="303" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C303" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="304" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C304" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="305" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C305" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="306" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C306" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="307" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C307" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="308" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C308" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="309" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C309" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="310" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C310" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="311" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C311" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="312" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C312" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="313" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C313" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="314" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C314" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="315" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C315" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="316" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C316" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="317" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C317" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="318" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C318" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="319" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C319" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="320" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C320" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="321" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C321" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="322" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C322" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="323" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C323" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="324" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C324" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="325" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C325" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="326" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C326" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="327" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C327" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="328" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C328" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="329" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C329" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="330" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C330" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="331" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C331" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="332" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C332" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="333" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C333" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="334" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C334" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="335" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C335" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="336" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C336" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="337" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C337" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="338" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C338" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="339" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C339" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="340" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C340" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="341" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C341" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="342" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C342" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="343" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C343" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="344" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C344" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="345" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C345" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="346" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C346" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="347" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C347" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="348" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C348" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="349" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C349" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="350" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C350" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="351" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C351" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="352" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C352" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="353" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C353" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="354" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C354" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="355" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C355" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="356" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C356" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="357" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C357" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="358" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C358" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="359" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C359" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="360" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C360" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="361" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C361" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="362" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C362" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="363" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C363" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="364" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C364" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="365" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C365" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="366" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C366" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="367" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C367" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="368" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C368" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="369" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C369" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="370" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C370" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="371" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C371" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="372" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C372" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="373" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C373" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="374" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C374" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="375" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C375" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="376" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C376" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="377" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C377" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="378" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C378" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="379" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C379" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="380" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C380" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="381" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C381" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="382" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C382" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="383" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C383" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="384" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C384" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="385" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C385" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="386" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C386" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="387" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C387" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="388" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C388" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="389" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C389" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="390" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C390" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="391" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C391" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="392" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C392" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="393" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C393" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="394" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C394" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="395" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C395" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="396" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C396" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="397" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C397" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="398" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C398" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="399" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C399" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="400" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C400" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="401" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C401" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="402" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C402" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="403" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C403" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="404" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C404" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="405" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C405" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="406" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C406" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="407" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C407" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="408" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C408" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="409" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C409" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="410" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C410" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="411" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C411" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="412" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C412" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="413" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C413" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="414" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C414" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="415" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C415" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="416" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C416" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="417" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C417" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="418" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C418" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="419" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C419" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="420" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C420" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="421" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C421" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="422" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C422" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="423" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C423" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="424" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C424" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="425" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C425" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="426" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C426" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="427" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C427" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="428" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C428" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="429" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C429" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="430" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C430" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="431" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C431" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="432" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C432" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="433" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C433" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="434" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C434" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="435" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C435" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="436" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C436" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="437" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C437" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="438" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C438" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="439" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C439" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="440" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C440" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="441" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C441" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="442" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C442" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="443" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C443" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="444" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C444" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="445" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C445" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="446" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C446" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="447" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C447" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="448" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C448" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="449" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C449" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="450" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C450" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="451" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C451" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="452" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C452" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="453" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C453" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="454" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C454" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="455" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C455" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="456" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C456" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="457" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C457" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="458" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C458" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="459" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C459" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="460" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C460" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="461" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C461" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="462" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C462" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="463" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C463" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="464" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C464" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="465" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C465" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="466" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C466" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="467" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C467" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="468" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C468" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="469" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C469" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="470" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C470" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="471" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C471" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="472" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C472" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="473" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C473" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="474" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C474" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="475" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C475" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="476" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C476" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="477" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C477" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="478" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C478" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="479" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C479" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="480" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C480" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="481" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C481" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="482" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C482" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="483" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C483" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="484" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C484" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="485" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C485" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="486" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C486" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="487" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C487" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="488" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C488" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="489" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C489" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="490" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C490" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="491" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C491" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="492" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C492" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="493" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C493" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="494" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C494" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="495" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C495" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="496" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C496" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="497" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C497" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="498" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C498" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="499" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C499" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="500" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C500" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="501" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C501" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="502" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C502" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="503" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C503" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="504" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C504" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="505" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C505" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="506" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C506" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="507" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C507" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="508" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C508" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="509" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C509" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="510" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C510" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="511" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C511" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="512" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C512" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="513" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C513" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="514" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C514" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="515" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C515" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="516" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C516" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="517" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C517" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="518" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C518" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="519" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C519" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="520" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C520" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="521" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C521" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="522" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C522" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="523" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C523" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="524" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C524" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="525" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C525" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="526" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C526" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="527" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C527" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="528" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C528" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="529" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C529" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="530" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C530" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="531" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C531" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="532" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C532" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="533" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C533" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="534" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C534" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="535" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C535" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="536" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C536" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="537" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C537" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="538" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C538" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="539" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C539" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="540" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C540" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="541" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C541" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="542" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C542" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="543" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C543" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="544" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C544" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="545" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C545" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="546" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C546" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="547" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C547" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="548" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C548" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="549" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C549" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="550" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C550" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="551" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C551" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="552" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C552" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="553" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C553" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="554" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C554" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="555" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C555" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="556" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C556" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="557" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C557" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="558" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C558" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="559" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C559" s="11" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="560" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C560" s="11" t="s">
+        <v>4970</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B101" xr:uid="{D6B3C0A2-850D-42EC-978A-945A59BF5661}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="although"/>
-        <filter val="approach"/>
-        <filter val="brought"/>
-        <filter val="cheap"/>
-        <filter val="concern"/>
-        <filter val="deal"/>
-        <filter val="due"/>
-        <filter val="either"/>
-        <filter val="even"/>
-        <filter val="ever"/>
-        <filter val="fell"/>
-        <filter val="filed"/>
-        <filter val="former"/>
-        <filter val="further"/>
-        <filter val="held"/>
-        <filter val="nearly"/>
-        <filter val="often"/>
-        <filter val="quiet"/>
-        <filter val="rather"/>
-        <filter val="rose"/>
-        <filter val="though"/>
-        <filter val="through"/>
-        <filter val="whether"/>
-        <filter val="whose"/>
-        <filter val="yet"/>
-      </filters>
+  <autoFilter ref="A1:C560" xr:uid="{D6B3C0A2-850D-42EC-978A-945A59BF5661}">
+    <filterColumn colId="2">
+      <filters blank="1"/>
     </filterColumn>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:A74">
-    <sortCondition ref="A1:A74"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:A66">
+    <sortCondition ref="A1:A66"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16838D2C-2B5C-4811-9CC1-2ED236D597F8}">
+  <dimension ref="D5:D35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="5" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D5" t="s">
+        <v>3027</v>
+      </c>
+    </row>
+    <row r="6" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D6" t="s">
+        <v>5108</v>
+      </c>
+    </row>
+    <row r="7" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D7" t="s">
+        <v>5109</v>
+      </c>
+    </row>
+    <row r="8" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D8" t="s">
+        <v>5110</v>
+      </c>
+    </row>
+    <row r="9" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D9" t="s">
+        <v>5111</v>
+      </c>
+    </row>
+    <row r="10" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D10" t="s">
+        <v>5112</v>
+      </c>
+    </row>
+    <row r="11" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D11" t="s">
+        <v>1561</v>
+      </c>
+    </row>
+    <row r="12" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D12" t="s">
+        <v>5113</v>
+      </c>
+    </row>
+    <row r="13" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D13" t="s">
+        <v>5114</v>
+      </c>
+    </row>
+    <row r="14" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D14" t="s">
+        <v>1715</v>
+      </c>
+    </row>
+    <row r="15" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D15" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="16" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D16" t="s">
+        <v>5115</v>
+      </c>
+    </row>
+    <row r="17" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D17" t="s">
+        <v>5116</v>
+      </c>
+    </row>
+    <row r="18" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D18" t="s">
+        <v>5117</v>
+      </c>
+    </row>
+    <row r="19" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D19" t="s">
+        <v>5118</v>
+      </c>
+    </row>
+    <row r="20" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D20" t="s">
+        <v>5119</v>
+      </c>
+    </row>
+    <row r="21" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D21" t="s">
+        <v>5120</v>
+      </c>
+    </row>
+    <row r="22" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D22" t="s">
+        <v>5121</v>
+      </c>
+    </row>
+    <row r="23" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D23" t="s">
+        <v>5122</v>
+      </c>
+    </row>
+    <row r="24" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D24" t="s">
+        <v>5123</v>
+      </c>
+    </row>
+    <row r="25" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D25" t="s">
+        <v>5124</v>
+      </c>
+    </row>
+    <row r="26" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D26" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="27" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D27" t="s">
+        <v>5125</v>
+      </c>
+    </row>
+    <row r="28" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D28" t="s">
+        <v>5126</v>
+      </c>
+    </row>
+    <row r="29" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D29" t="s">
+        <v>5127</v>
+      </c>
+    </row>
+    <row r="30" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D30" t="s">
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="31" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D31" t="s">
+        <v>5128</v>
+      </c>
+    </row>
+    <row r="32" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D32" t="s">
+        <v>5129</v>
+      </c>
+    </row>
+    <row r="33" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D33" t="s">
+        <v>5130</v>
+      </c>
+    </row>
+    <row r="34" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D34" t="s">
+        <v>5131</v>
+      </c>
+    </row>
+    <row r="35" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D35" t="s">
+        <v>5132</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>